--- a/berekeningen/berekeningen borstelmotorvermogen.xlsx
+++ b/berekeningen/berekeningen borstelmotorvermogen.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://saxion.sharepoint.com/teams/O365-Course-Team-113290-group5.0/Shared Documents/group 5/berekeningen/"/>
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,24 +41,24 @@
     <t>inputs:</t>
   </si>
   <si>
+    <t>berekeningen</t>
+  </si>
+  <si>
+    <t>grootheid</t>
+  </si>
+  <si>
+    <t>waarde</t>
+  </si>
+  <si>
+    <t>eenheid</t>
+  </si>
+  <si>
     <t>toerental</t>
   </si>
   <si>
-    <t>grootheid</t>
-  </si>
-  <si>
-    <t>waarde</t>
-  </si>
-  <si>
-    <t>eenheid</t>
-  </si>
-  <si>
     <t>rpm</t>
   </si>
   <si>
-    <t>berekeningen</t>
-  </si>
-  <si>
     <t>rad/s</t>
   </si>
   <si>
@@ -68,37 +68,37 @@
     <t>-</t>
   </si>
   <si>
+    <t>Fz</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>kilo</t>
   </si>
   <si>
-    <t>Fz</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>radius borstel</t>
   </si>
   <si>
+    <t>m</t>
+  </si>
+  <si>
     <t>cm</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>koppel op borstel</t>
   </si>
   <si>
     <t>Nm</t>
   </si>
   <si>
+    <t>weerstand in lagering</t>
+  </si>
+  <si>
+    <t>verwaarloosbaar</t>
+  </si>
+  <si>
     <t>vermogen borstel</t>
-  </si>
-  <si>
-    <t>weerstand in lagering</t>
-  </si>
-  <si>
-    <t>verwaarloosbaar</t>
   </si>
   <si>
     <t>Watt</t>
@@ -108,7 +108,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,7 +141,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -474,22 +474,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C009ED-5E6C-4437-ADB2-7E2E436960C3}">
   <dimension ref="B2:H8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:8">
       <c r="B3" t="s">
         <v>2</v>
       </c>
@@ -509,18 +509,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>3000</v>
       </c>
       <c r="D4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
         <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1</v>
       </c>
       <c r="G4">
         <f>C4*2*PI()/60</f>
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -541,25 +541,25 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <f>C6*9.81</f>
         <v>29.43</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
@@ -569,10 +569,10 @@
         <v>0.04</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8">
       <c r="B7" t="s">
         <v>13</v>
       </c>
@@ -580,7 +580,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -593,18 +593,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8">
       <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" t="s">
         <v>19</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
       </c>
       <c r="D8" t="s">
         <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8">
         <f>G7*G4</f>
@@ -620,8 +620,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E64CE4358CF9434AACD5F17CD166EEBE" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="73a9dcd17d910bedbbfcf71dea21917b">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71fe66e1-c1d4-4b45-94dc-995258161867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a2fda66a0a1023ae4e3cd4e4288c789" ns2:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71fe66e1-c1d4-4b45-94dc-995258161867">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E64CE4358CF9434AACD5F17CD166EEBE" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="76f0660c00307a9fc6b8f016be658328">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71fe66e1-c1d4-4b45-94dc-995258161867" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47a6827155b2c9d8b55185a8ae1cad52" ns2:_="">
     <xsd:import namespace="71fe66e1-c1d4-4b45-94dc-995258161867"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -791,27 +810,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="71fe66e1-c1d4-4b45-94dc-995258161867">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC6C57BE-6D11-4D2E-ABB4-D9149EDC80CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73564561-12B4-404A-8A26-D1E02562C754}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -819,5 +819,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73564561-12B4-404A-8A26-D1E02562C754}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{353DB637-5244-43ED-B9F7-0CEE4634DFA9}"/>
 </file>